--- a/Deliverables/sprint-04/planning-documents.xlsx
+++ b/Deliverables/sprint-04/planning-documents.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="291">
   <si>
     <t>Project Name</t>
   </si>
@@ -397,7 +397,7 @@
     <t xml:space="preserve">E2E </t>
   </si>
   <si>
-    <t>End-to-End Workflow: The complete processing pipeline of a system interaction, starting from user input through internal processing and concluding with the system’s resulting output.</t>
+    <t>End-to-End (Workflow): The complete processing pipeline of a system interaction, starting from user input through internal processing and concluding with the system’s resulting output.</t>
   </si>
   <si>
     <t>LLM (Large Language Model)</t>
@@ -448,7 +448,7 @@
     <t>Optional</t>
   </si>
   <si>
-    <t>E2E Single Prompt Agent Prototype</t>
+    <t>Persistent Single-Prompt Agent Prototype and Cloud Environment Preparation</t>
   </si>
   <si>
     <t>Sprint</t>
@@ -1022,7 +1022,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -1265,6 +1265,9 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -1654,8 +1657,8 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="137829145"/>
-        <c:axId val="464189944"/>
+        <c:axId val="1010223247"/>
+        <c:axId val="1072654810"/>
       </c:barChart>
       <c:lineChart>
         <c:varyColors val="0"/>
@@ -1690,11 +1693,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="137829145"/>
-        <c:axId val="464189944"/>
+        <c:axId val="1010223247"/>
+        <c:axId val="1072654810"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="137829145"/>
+        <c:axId val="1010223247"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1746,10 +1749,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="464189944"/>
+        <c:crossAx val="1072654810"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="464189944"/>
+        <c:axId val="1072654810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1824,7 +1827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="137829145"/>
+        <c:crossAx val="1010223247"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1919,8 +1922,8 @@
           </c:val>
         </c:ser>
         <c:overlap val="100"/>
-        <c:axId val="1778514594"/>
-        <c:axId val="1042068790"/>
+        <c:axId val="230225639"/>
+        <c:axId val="900347603"/>
       </c:barChart>
       <c:lineChart>
         <c:varyColors val="0"/>
@@ -1957,11 +1960,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1778514594"/>
-        <c:axId val="1042068790"/>
+        <c:axId val="230225639"/>
+        <c:axId val="900347603"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1778514594"/>
+        <c:axId val="230225639"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2013,10 +2016,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1042068790"/>
+        <c:crossAx val="900347603"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1042068790"/>
+        <c:axId val="900347603"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2091,7 +2094,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1778514594"/>
+        <c:crossAx val="230225639"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2595,7 +2598,7 @@
       <c r="A1" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="85" t="s">
         <v>141</v>
       </c>
       <c r="C1" s="47" t="s">
@@ -2673,7 +2676,7 @@
       <c r="A7" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="85"/>
+      <c r="B7" s="86"/>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
       <c r="E7" s="60"/>
@@ -2685,11 +2688,11 @@
       <c r="B8" s="51"/>
       <c r="C8" s="51"/>
       <c r="D8" s="51"/>
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="87" t="s">
         <v>170</v>
       </c>
       <c r="F8" s="51"/>
-      <c r="G8" s="86" t="s">
+      <c r="G8" s="87" t="s">
         <v>171</v>
       </c>
     </row>
@@ -2833,7 +2836,7 @@
     </row>
     <row r="18">
       <c r="A18" s="49"/>
-      <c r="B18" s="87"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="66"/>
       <c r="D18" s="75"/>
       <c r="E18" s="50"/>
@@ -2975,7 +2978,7 @@
     <row r="33">
       <c r="A33" s="63"/>
       <c r="B33" s="30"/>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="89" t="s">
         <v>167</v>
       </c>
       <c r="D33" s="57"/>
@@ -3014,7 +3017,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="90" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="46" t="s">
@@ -3023,7 +3026,7 @@
       <c r="C1" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="90" t="s">
+      <c r="D1" s="91" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3960,308 +3963,308 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="91" t="str">
+      <c r="A1" s="92" t="str">
         <f>'Project Team'!A1</f>
         <v>Last Name</v>
       </c>
-      <c r="B1" s="91" t="str">
+      <c r="B1" s="92" t="str">
         <f>'Project Team'!B1</f>
         <v>First Name</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="93" t="s">
         <v>278</v>
       </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
     </row>
     <row r="2">
-      <c r="A2" s="97" t="str">
+      <c r="A2" s="98" t="str">
         <f>'Project Team'!A2</f>
         <v>Fatima</v>
       </c>
-      <c r="B2" s="97" t="str">
+      <c r="B2" s="98" t="str">
         <f>'Project Team'!B2</f>
         <v>Qiblatain</v>
       </c>
-      <c r="C2" s="98">
+      <c r="C2" s="99">
         <v>0.0</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="100">
+      <c r="D2" s="100"/>
+      <c r="E2" s="101">
         <f>average(C2:C10)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="101" t="str">
+      <c r="F2" s="102" t="str">
         <f>if(stdev(C2:C7) &gt; 0,"NOK", "OK")</f>
         <v>OK</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
     </row>
     <row r="3">
-      <c r="A3" s="103" t="str">
+      <c r="A3" s="104" t="str">
         <f>'Project Team'!A3</f>
         <v>Huy</v>
       </c>
-      <c r="B3" s="103" t="str">
+      <c r="B3" s="104" t="str">
         <f>'Project Team'!B3</f>
         <v>Christoph</v>
       </c>
-      <c r="C3" s="98">
+      <c r="C3" s="99">
         <v>0.0</v>
       </c>
-      <c r="D3" s="104"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
     </row>
     <row r="4">
-      <c r="A4" s="97" t="str">
+      <c r="A4" s="98" t="str">
         <f>'Project Team'!A4</f>
         <v>Raza</v>
       </c>
-      <c r="B4" s="97" t="str">
+      <c r="B4" s="98" t="str">
         <f>'Project Team'!B4</f>
         <v>Asad</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="99"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="100"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
     </row>
     <row r="5">
-      <c r="A5" s="103" t="str">
+      <c r="A5" s="104" t="str">
         <f>'Project Team'!A5</f>
         <v>Jokiel</v>
       </c>
-      <c r="B5" s="103" t="str">
+      <c r="B5" s="104" t="str">
         <f>'Project Team'!B5</f>
         <v>Rene</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
     </row>
     <row r="6">
-      <c r="A6" s="97" t="str">
+      <c r="A6" s="98" t="str">
         <f>'Project Team'!A6</f>
         <v>Mosler</v>
       </c>
-      <c r="B6" s="97" t="str">
+      <c r="B6" s="98" t="str">
         <f>'Project Team'!B6</f>
         <v>Carl</v>
       </c>
-      <c r="C6" s="98"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="110">
+      <c r="C6" s="99"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111">
         <v>0.0</v>
       </c>
-      <c r="F6" s="111" t="s">
+      <c r="F6" s="112" t="s">
         <v>279</v>
       </c>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
     </row>
     <row r="7">
-      <c r="A7" s="103" t="str">
+      <c r="A7" s="104" t="str">
         <f>'Project Team'!A7</f>
         <v>Vineesh</v>
       </c>
-      <c r="B7" s="103" t="str">
+      <c r="B7" s="104" t="str">
         <f>'Project Team'!B7</f>
         <v>Koppay</v>
       </c>
-      <c r="C7" s="106"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="110">
+      <c r="C7" s="107"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="111">
         <v>1.0</v>
       </c>
-      <c r="F7" s="111" t="s">
+      <c r="F7" s="112" t="s">
         <v>280</v>
       </c>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
     </row>
     <row r="8">
-      <c r="A8" s="97" t="str">
+      <c r="A8" s="98" t="str">
         <f>'Project Team'!A8</f>
         <v>Moeez</v>
       </c>
-      <c r="B8" s="97" t="str">
+      <c r="B8" s="98" t="str">
         <f>'Project Team'!B8</f>
         <v>Abdul</v>
       </c>
-      <c r="C8" s="107"/>
-      <c r="D8" s="109"/>
-      <c r="E8" s="110">
+      <c r="C8" s="108"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="111">
         <v>2.0</v>
       </c>
-      <c r="F8" s="111" t="s">
+      <c r="F8" s="112" t="s">
         <v>281</v>
       </c>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
     </row>
     <row r="9">
-      <c r="A9" s="103" t="str">
+      <c r="A9" s="104" t="str">
         <f>'Project Team'!A9</f>
         <v>Thakur</v>
       </c>
-      <c r="B9" s="103" t="str">
+      <c r="B9" s="104" t="str">
         <f>'Project Team'!B9</f>
         <v>Shikhar</v>
       </c>
-      <c r="C9" s="107"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="110">
+      <c r="C9" s="108"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="111">
         <v>3.0</v>
       </c>
-      <c r="F9" s="111" t="s">
+      <c r="F9" s="112" t="s">
         <v>282</v>
       </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="106"/>
     </row>
     <row r="10">
-      <c r="A10" s="97" t="str">
+      <c r="A10" s="98" t="str">
         <f>'Project Team'!A10</f>
         <v>Dhruvin</v>
       </c>
-      <c r="B10" s="97" t="str">
+      <c r="B10" s="98" t="str">
         <f>'Project Team'!B10</f>
         <v>Vekariya</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="109"/>
-      <c r="E10" s="110">
+      <c r="C10" s="108"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="111">
         <v>5.0</v>
       </c>
-      <c r="F10" s="111" t="s">
+      <c r="F10" s="112" t="s">
         <v>283</v>
       </c>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
     </row>
     <row r="11">
-      <c r="A11" s="103"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="108"/>
-      <c r="E11" s="110">
+      <c r="A11" s="104"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="111">
         <v>8.0</v>
       </c>
-      <c r="F11" s="111" t="s">
+      <c r="F11" s="112" t="s">
         <v>284</v>
       </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="106"/>
     </row>
     <row r="12">
-      <c r="A12" s="97"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="106"/>
-      <c r="D12" s="109"/>
-      <c r="E12" s="110">
+      <c r="A12" s="98"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="111">
         <v>13.0</v>
       </c>
-      <c r="F12" s="111" t="s">
+      <c r="F12" s="112" t="s">
         <v>285</v>
       </c>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
     </row>
     <row r="13">
-      <c r="A13" s="103"/>
-      <c r="B13" s="103"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
     </row>
     <row r="14">
-      <c r="A14" s="112" t="s">
+      <c r="A14" s="113" t="s">
         <v>286</v>
       </c>
-      <c r="B14" s="113"/>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
     </row>
     <row r="15">
-      <c r="A15" s="114"/>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
     </row>
     <row r="16">
-      <c r="A16" s="115" t="s">
+      <c r="A16" s="116" t="s">
         <v>287</v>
       </c>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="116"/>
-      <c r="H16" s="116"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
     </row>
     <row r="17">
-      <c r="A17" s="117" t="s">
+      <c r="A17" s="118" t="s">
         <v>288</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
     </row>
     <row r="18">
-      <c r="A18" s="115" t="s">
+      <c r="A18" s="116" t="s">
         <v>289</v>
       </c>
-      <c r="B18" s="116"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="116"/>
+      <c r="B18" s="117"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
     </row>
     <row r="19">
-      <c r="A19" s="114"/>
-      <c r="B19" s="114"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="114"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="114"/>
+      <c r="A19" s="115"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
     </row>
     <row r="20">
-      <c r="A20" s="116"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
+      <c r="A20" s="117"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4317,7 +4320,7 @@
       <c r="L1" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="M1" s="118" t="s">
+      <c r="M1" s="119" t="s">
         <v>290</v>
       </c>
     </row>
@@ -4329,7 +4332,7 @@
         <f>'Velocity Tracking'!B2</f>
         <v>1</v>
       </c>
-      <c r="C2" s="119">
+      <c r="C2" s="120">
         <f t="shared" ref="C2:C16" si="1">AVERAGE($B$2:$B$16)</f>
         <v>10.66666667</v>
       </c>
@@ -4340,7 +4343,7 @@
       <c r="J2" s="51"/>
       <c r="K2" s="51"/>
       <c r="L2" s="51"/>
-      <c r="M2" s="120"/>
+      <c r="M2" s="121"/>
     </row>
     <row r="3">
       <c r="A3" s="43">
@@ -4351,7 +4354,7 @@
         <f>'Velocity Tracking'!B3</f>
         <v>12</v>
       </c>
-      <c r="C3" s="119">
+      <c r="C3" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4364,7 +4367,7 @@
       <c r="J3" s="54"/>
       <c r="K3" s="54"/>
       <c r="L3" s="54"/>
-      <c r="M3" s="121"/>
+      <c r="M3" s="122"/>
     </row>
     <row r="4">
       <c r="A4" s="43">
@@ -4375,7 +4378,7 @@
         <f>'Velocity Tracking'!B4</f>
         <v>19</v>
       </c>
-      <c r="C4" s="119">
+      <c r="C4" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4386,7 +4389,7 @@
       <c r="J4" s="51"/>
       <c r="K4" s="51"/>
       <c r="L4" s="51"/>
-      <c r="M4" s="120"/>
+      <c r="M4" s="121"/>
     </row>
     <row r="5">
       <c r="A5" s="43">
@@ -4397,7 +4400,7 @@
         <f>'Velocity Tracking'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="119">
+      <c r="C5" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4416,7 +4419,7 @@
       </c>
       <c r="K5" s="30"/>
       <c r="L5" s="30"/>
-      <c r="M5" s="122">
+      <c r="M5" s="123">
         <f>I5/6</f>
         <v>11</v>
       </c>
@@ -4430,7 +4433,7 @@
         <f>'Velocity Tracking'!B6</f>
         <v/>
       </c>
-      <c r="C6" s="119">
+      <c r="C6" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4441,7 +4444,7 @@
       <c r="J6" s="51"/>
       <c r="K6" s="51"/>
       <c r="L6" s="51"/>
-      <c r="M6" s="120"/>
+      <c r="M6" s="121"/>
     </row>
     <row r="7">
       <c r="A7" s="43">
@@ -4452,7 +4455,7 @@
         <f>'Velocity Tracking'!B7</f>
         <v/>
       </c>
-      <c r="C7" s="119">
+      <c r="C7" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4465,7 +4468,7 @@
       <c r="J7" s="60"/>
       <c r="K7" s="60"/>
       <c r="L7" s="60"/>
-      <c r="M7" s="123"/>
+      <c r="M7" s="124"/>
     </row>
     <row r="8">
       <c r="A8" s="43">
@@ -4476,7 +4479,7 @@
         <f>'Velocity Tracking'!B8</f>
         <v/>
       </c>
-      <c r="C8" s="119">
+      <c r="C8" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4493,7 +4496,7 @@
       <c r="L8" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="M8" s="124" t="str">
+      <c r="M8" s="125" t="str">
         <f>"Development Speed (≈" &amp; ROUND(M5, 0) &amp; " SP/s)"</f>
         <v>Development Speed (≈11 SP/s)</v>
       </c>
@@ -4507,7 +4510,7 @@
         <f>'Velocity Tracking'!B9</f>
         <v/>
       </c>
-      <c r="C9" s="119">
+      <c r="C9" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4532,7 +4535,7 @@
         <f>'Mid-Project Release plan'!G9</f>
         <v>66</v>
       </c>
-      <c r="M9" s="125">
+      <c r="M9" s="126">
         <f>$I$5</f>
         <v>66</v>
       </c>
@@ -4546,7 +4549,7 @@
         <f>'Velocity Tracking'!B10</f>
         <v/>
       </c>
-      <c r="C10" s="119">
+      <c r="C10" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4572,7 +4575,7 @@
         <f>'Mid-Project Release plan'!G10</f>
         <v>65</v>
       </c>
-      <c r="M10" s="125">
+      <c r="M10" s="126">
         <f t="shared" ref="M10:M15" si="4">M9-$M$5</f>
         <v>55</v>
       </c>
@@ -4586,7 +4589,7 @@
         <f>'Velocity Tracking'!B11</f>
         <v/>
       </c>
-      <c r="C11" s="119">
+      <c r="C11" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4612,7 +4615,7 @@
         <f>'Mid-Project Release plan'!G11</f>
         <v>53</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="126">
         <f t="shared" si="4"/>
         <v>44</v>
       </c>
@@ -4626,7 +4629,7 @@
         <f>'Velocity Tracking'!B12</f>
         <v/>
       </c>
-      <c r="C12" s="119">
+      <c r="C12" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4651,7 +4654,7 @@
         <f>'Mid-Project Release plan'!G12</f>
         <v>35</v>
       </c>
-      <c r="M12" s="125">
+      <c r="M12" s="126">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
@@ -4665,7 +4668,7 @@
         <f>'Velocity Tracking'!B13</f>
         <v/>
       </c>
-      <c r="C13" s="119">
+      <c r="C13" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4690,7 +4693,7 @@
         <f>'Mid-Project Release plan'!G13</f>
         <v>35</v>
       </c>
-      <c r="M13" s="125">
+      <c r="M13" s="126">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
@@ -4704,7 +4707,7 @@
         <f>'Velocity Tracking'!B14</f>
         <v/>
       </c>
-      <c r="C14" s="119">
+      <c r="C14" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4727,7 +4730,7 @@
         <f>'Mid-Project Release plan'!G14</f>
         <v>35</v>
       </c>
-      <c r="M14" s="125">
+      <c r="M14" s="126">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
@@ -4741,7 +4744,7 @@
         <f>'Velocity Tracking'!B15</f>
         <v/>
       </c>
-      <c r="C15" s="119">
+      <c r="C15" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -4766,7 +4769,7 @@
         <f>'Mid-Project Release plan'!G15</f>
         <v/>
       </c>
-      <c r="M15" s="125">
+      <c r="M15" s="126">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4780,7 +4783,7 @@
         <f>'Velocity Tracking'!B16</f>
         <v/>
       </c>
-      <c r="C16" s="119">
+      <c r="C16" s="120">
         <f t="shared" si="1"/>
         <v>10.66666667</v>
       </c>
@@ -5741,6 +5744,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="12.75"/>
   <cols>
@@ -5861,6 +5865,9 @@
       <c r="B20" s="3"/>
     </row>
   </sheetData>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
@@ -5872,6 +5879,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="12.75"/>
   <cols>
@@ -6018,6 +6026,9 @@
       <c r="B20" s="3"/>
     </row>
   </sheetData>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
@@ -6033,7 +6044,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="12.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="6.38"/>
-    <col customWidth="1" min="2" max="2" width="28.0"/>
+    <col customWidth="1" min="2" max="2" width="36.75"/>
     <col customWidth="1" min="3" max="3" width="62.63"/>
     <col customWidth="1" min="4" max="7" width="15.75"/>
   </cols>
@@ -6538,8 +6549,9 @@
       <c r="A36" s="65">
         <v>4.0</v>
       </c>
-      <c r="B36" s="73" t="s">
-        <v>138</v>
+      <c r="B36" s="73" t="str">
+        <f>'Sprint Goals'!B5</f>
+        <v>Optional</v>
       </c>
       <c r="C36" s="66" t="s">
         <v>161</v>
@@ -6629,9 +6641,9 @@
       <c r="A43" s="63">
         <v>5.0</v>
       </c>
-      <c r="B43" s="79" t="str">
+      <c r="B43" s="81" t="str">
         <f>'Sprint Goals'!B6</f>
-        <v>E2E Single Prompt Agent Prototype</v>
+        <v>Persistent Single-Prompt Agent Prototype and Cloud Environment Preparation</v>
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="57"/>
@@ -6685,7 +6697,7 @@
       <c r="G48" s="66"/>
     </row>
     <row r="49">
-      <c r="A49" s="81"/>
+      <c r="A49" s="82"/>
       <c r="B49" s="79"/>
       <c r="C49" s="30"/>
       <c r="D49" s="57"/>
@@ -6833,7 +6845,7 @@
     <row r="65">
       <c r="A65" s="63"/>
       <c r="B65" s="74"/>
-      <c r="C65" s="82" t="s">
+      <c r="C65" s="83" t="s">
         <v>167</v>
       </c>
       <c r="D65" s="57"/>
@@ -6993,7 +7005,7 @@
     </row>
     <row r="18">
       <c r="A18" s="43"/>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="84" t="s">
         <v>169</v>
       </c>
     </row>
